--- a/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKKLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>BKKLY</t>
   </si>
@@ -656,71 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -763,8 +769,14 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +819,14 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +869,14 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,8 +893,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -913,8 +939,14 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,8 +989,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1001,8 +1039,14 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,8 +1089,14 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1060,8 +1110,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1104,8 +1156,14 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,8 +1206,14 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,8 +1230,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1210,8 +1276,14 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1254,8 +1326,14 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1298,8 +1376,14 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1342,8 +1426,14 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1386,8 +1476,14 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,8 +1526,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1474,8 +1576,14 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1518,8 +1626,14 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1562,8 +1676,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1606,8 +1726,14 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,8 +1776,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1694,8 +1826,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1738,8 +1876,14 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1782,8 +1926,14 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1826,8 +1976,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1870,57 +2026,69 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1937,8 +2105,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1955,96 +2125,110 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1185000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1230800</v>
+      </c>
+      <c r="F41" s="3">
         <v>1508100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1175600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1166800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1296600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1379900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1294000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1053000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1144500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1324000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1094200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1210900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1369500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1516800</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3020800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3033600</v>
+      </c>
+      <c r="F42" s="3">
         <v>3551800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>3221400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>3234300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2657300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>2999100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>7596900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2832300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>3050200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2474800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2995600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>2639200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>2266800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2602900</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2087,272 +2271,314 @@
       <c r="P43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>162600</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>164300</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>237900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>313000</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3">
         <v>341100</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>347200</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>785200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>323700</v>
+      </c>
+      <c r="F45" s="3">
         <v>173400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>358900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>829500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>352000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>234200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>509600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>272800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>612800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>364500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>703200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>322000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>765400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>293700</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4489300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4588200</v>
+      </c>
+      <c r="F46" s="3">
         <v>5395900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4755900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4761700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4305900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4777600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9400600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4396000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4807600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4476300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4792900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4513200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4401800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4760600</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>60084000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>62576900</v>
+      </c>
+      <c r="F47" s="3">
         <v>62508800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>59220400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>57965500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>56062900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>53409100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>50961500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>47689300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>48119200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>52512000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>47540800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>49214200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>52596200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>48816600</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2114700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2186300</v>
+      </c>
+      <c r="F48" s="3">
         <v>2267200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2237400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2265300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1745700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1750900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1875300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1691200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1707600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1801300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1726000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1785900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1806600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1790400</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>641100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>693400</v>
+      </c>
+      <c r="F49" s="3">
         <v>714000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>759300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>797100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>789300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>809900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>949200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>919400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>939500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>966200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>967200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1002700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1005700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>974800</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2621,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2439,52 +2671,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1692000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1497200</v>
+      </c>
+      <c r="F52" s="3">
         <v>1300300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1141900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1120100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1118700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1022800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1497500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1453700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1465800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1063100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1901900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1094700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>783700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>808400</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,52 +2771,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>140757300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>144287000</v>
+      </c>
+      <c r="F54" s="3">
         <v>146061500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>139756600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>141936800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>136293100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>132604400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>138386900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>123316900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>125486400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>131315200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>124700800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>127021100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>130963400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>127910900</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,8 +2845,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2607,272 +2865,310 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>98069400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>98773100</v>
+      </c>
+      <c r="F57" s="3">
         <v>103203400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>97748600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>98404700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>94971300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>93925500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>96171100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>87779400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>88074400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>93829500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>86521100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>91812500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>94116600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>94581700</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3132400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2148200</v>
+      </c>
+      <c r="F58" s="3">
         <v>2109800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1879000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2893100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1749000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2659300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2255500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2595200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2429500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2481300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2958000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3546000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1760100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2589700</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9086000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>263000</v>
+      </c>
+      <c r="F59" s="3">
         <v>7916100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>177700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>208000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>222600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>8360300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>223200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>221000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>212800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>7800300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>176300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6922000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>228600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5763100</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>111101900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>101186200</v>
+      </c>
+      <c r="F60" s="3">
         <v>114172200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>99807400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>102272000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>96945000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>105669700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>98653600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>91368200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>90718400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>104893500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>89656900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>103051300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>96106900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>103527700</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6892200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7748100</v>
+      </c>
+      <c r="F61" s="3">
         <v>7716000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6595900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6613400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7341700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5454400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6401600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5536400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5579700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5545800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6656600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4331200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5452800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4910700</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4790100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>17584800</v>
+      </c>
+      <c r="F62" s="3">
         <v>5404200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>15297700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>14880500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>15362300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>4817600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>16305200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>11112600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>13832300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5012900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>13889300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>4429600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>14217500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4381000</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2915,8 +3211,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2959,8 +3261,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3003,52 +3311,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>123279100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>126521400</v>
+      </c>
+      <c r="F66" s="3">
         <v>127807300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>121702800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>124238400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>119649000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>116379900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>121360600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>108421000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>110132100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>115874600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>110205800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>112224700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>115781600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>113240500</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3065,8 +3385,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3109,8 +3431,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3153,8 +3481,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3197,8 +3531,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3241,52 +3581,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14318800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>14775300</v>
+      </c>
+      <c r="F72" s="3">
         <v>14933200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>14260500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>13975400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>13380000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>12862900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>13317000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>11483800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>11548900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>11904600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>10932500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>11097500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>11338500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>10867200</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3329,8 +3681,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3373,8 +3731,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3417,52 +3781,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17425100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>17708000</v>
+      </c>
+      <c r="F76" s="3">
         <v>18198400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>18001200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>17644200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16588400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16171100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>16971500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14844600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15299000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>15386600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>14444800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>14742400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>15124700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14618500</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3505,57 +3881,69 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3598,8 +3986,14 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,52 +4010,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>42200</v>
+      </c>
+      <c r="F83" s="3">
         <v>11100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>44500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>40700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>36200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>18900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>34500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>34700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>35100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>23200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>34800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>38800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>43200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3704,8 +4106,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3748,8 +4156,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3792,8 +4206,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3836,8 +4256,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3880,52 +4306,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-98100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1108400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-449000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>5971900</v>
       </c>
-      <c r="F89" s="3">
-        <v>-757400</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-753500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1898300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-3194800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>3100800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>536400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1057500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>334300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1367800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>556000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1689600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1107500</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3942,52 +4380,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-12600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-21400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-14300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-10700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-17200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-17900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-39600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-26200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-12000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-9100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-12500</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4030,8 +4476,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4074,52 +4526,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>888200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2163700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1056200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4425400</v>
       </c>
-      <c r="F94" s="3">
-        <v>1867400</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>1863500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-826100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>1628500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1374900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>28200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-944400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-245700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1566800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-321200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1704500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4136,52 +4600,60 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
+        <v>459100</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>117600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>382000</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>118000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>259800</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>104400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>162100</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4224,8 +4696,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4268,8 +4746,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4312,136 +4796,160 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-814200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>827700</v>
+      </c>
+      <c r="F100" s="3">
         <v>1803900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1537400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1298700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>2624900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1726400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1623000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-643600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-224000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>73800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>122900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-346000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-153800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1298500</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-226500</v>
+      </c>
+      <c r="F102" s="3">
         <v>297500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>8700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-188900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-98100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>160800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>97800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-78400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-108900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>160400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-75500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-110100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-169700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>246000</v>
       </c>
     </row>
